--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3747.87</v>
+        <v>3728.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1131.58</v>
+        <v>1125.76</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5585.55</v>
+        <v>5527.06</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1141.55</v>
+        <v>1129.59</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5624.52</v>
+        <v>5685.7</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2925.31</v>
+        <v>2957.12</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1402.56</v>
+        <v>1417.81</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2669.72</v>
+        <v>2678.5</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1149.3</v>
+        <v>1169.14</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5004.75</v>
+        <v>5028.06</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3293.5</v>
+        <v>3308.84</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>17746.51</v>
+        <v>17874.45</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5461.87</v>
+        <v>5501.25</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8081.52</v>
+        <v>8067.18</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1797.56</v>
+        <v>1794.37</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4807.44</v>
+        <v>4832.27</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6880.51</v>
+        <v>6929.07</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2737.36</v>
+        <v>2701.98</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8486.07</v>
+        <v>8376.389999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>929.37</v>
+        <v>917.5700000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3136.34</v>
+        <v>3096.5</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>102325.45</v>
+        <v>101307.36</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9493.41</v>
+        <v>9398.959999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7749.53</v>
+        <v>7672.42</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2074.25</v>
+        <v>2066.81</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3787.79</v>
+        <v>3774.2</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1262.47</v>
+        <v>1259.74</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2647.51</v>
+        <v>2616.87</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27506.02</v>
+        <v>27187.69</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7060.06</v>
+        <v>6978.35</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1685.97</v>
+        <v>1666.45</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2666.16</v>
+        <v>2643.58</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1149.13</v>
+        <v>1153.54</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3162.27</v>
+        <v>3174.4</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>769.5</v>
+        <v>772.46</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22523.43</v>
+        <v>22625.5</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2807.69</v>
+        <v>2811.29</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2314.73</v>
+        <v>2330.67</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8416.92</v>
+        <v>8488.85</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1238.76</v>
+        <v>1249.34</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>786.66</v>
+        <v>793.39</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6032.07</v>
+        <v>6065.06</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2145.35</v>
+        <v>2118.12</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8248.360000000001</v>
+        <v>8129.5</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>14713.9</v>
+        <v>14937.9</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3984.51</v>
+        <v>4045.17</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3814.69</v>
+        <v>3872.77</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5437.58</v>
+        <v>5520.36</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>27839.54</v>
+        <v>28543.33</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8889.67</v>
+        <v>9159.23</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1725.84</v>
+        <v>1778.17</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2794.42</v>
+        <v>2879.16</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6023.5</v>
+        <v>6002.05</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>28996.05</v>
+        <v>28779.05</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3124.57</v>
+        <v>3133.63</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1406.83</v>
+        <v>1400.9</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1446.59</v>
+        <v>1450.56</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2638.55</v>
+        <v>2655.93</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>818.35</v>
+        <v>823.74</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1089.44</v>
+        <v>1099.14</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4099.02</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3827.82</v>
+        <v>3823.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2331.36</v>
+        <v>2314.66</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2536.87</v>
+        <v>2521.46</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1187.07</v>
+        <v>1182.49</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1401.52</v>
+        <v>1402.87</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3975.68</v>
+        <v>3979.51</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3376.28</v>
+        <v>3474.35</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8399.110000000001</v>
+        <v>8643.07</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3780.47</v>
+        <v>3795.38</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4736.29</v>
+        <v>4675.31</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1726.36</v>
+        <v>1714.17</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1566.18</v>
+        <v>1555.12</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1175.75</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2509.89</v>
+        <v>2549.2</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1250.59</v>
+        <v>1270.18</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1095.62</v>
+        <v>1095.56</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2960.18</v>
+        <v>2960.03</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>961.55</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2104.64</v>
+        <v>2113.34</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>820.8</v>
+        <v>818.54</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>23653.57</v>
+        <v>23588.32</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3267.02</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2191.91</v>
+        <v>2166.61</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1903.5</v>
+        <v>1891.3</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5338.1</v>
+        <v>5260.88</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1246.62</v>
+        <v>1222.04</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8100.1</v>
+        <v>7940.35</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>16673.91</v>
+        <v>16345.08</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1721.87</v>
+        <v>1726.88</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>860.45</v>
+        <v>867.75</v>
       </c>
     </row>
     <row r="93">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4118.43</v>
+        <v>4172.17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2778-159-CM26</t>
+          <t>4737-48-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1008.33</v>
+        <v>5361.55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2778-160-CM26</t>
+          <t>4590-6-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1831.28</v>
+        <v>22557.67</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4590-6-CM26</t>
+          <t>2778-160-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6268,17 +6268,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>22304.02</v>
+        <v>1852.11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4737-48-CM26</t>
+          <t>2778-159-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5301.26</v>
+        <v>1019.8</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6723.66</v>
+        <v>6784.23</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>786.77</v>
+        <v>793.86</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4637.59</v>
+        <v>4656.81</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1071.8</v>
+        <v>1076.24</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1246.62</v>
+        <v>1249.2</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1806.43</v>
+        <v>1810.17</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>939.53</v>
+        <v>935.5</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>16930.46</v>
+        <v>16700.28</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12237.33</v>
+        <v>12132.96</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>788.63</v>
+        <v>792.88</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6162.33</v>
+        <v>6195.51</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3437.31</v>
+        <v>3450.33</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1040.37</v>
+        <v>1050.26</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4968.24</v>
+        <v>4918.69</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1259.69</v>
+        <v>1245.99</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4918.36</v>
+        <v>4934.67</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1623.09</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3951.81</v>
+        <v>3998.16</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3999.66</v>
+        <v>3969.32</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6258.4</v>
+        <v>6152.66</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2406.6</v>
+        <v>2372.45</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1144.75</v>
+        <v>1129.5</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1654.62</v>
+        <v>1620.62</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>40602.81</v>
+        <v>40761.31</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5101.89</v>
+        <v>5153.2</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1026.54</v>
+        <v>1031.77</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5124.5</v>
+        <v>5144.45</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2749.79</v>
+        <v>2760.5</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8114.63</v>
+        <v>8073.52</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2935.2</v>
+        <v>2920.33</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>837.36</v>
+        <v>842.8200000000001</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1747.48</v>
+        <v>1758.87</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1002.3</v>
+        <v>1009.31</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1759.93</v>
+        <v>1772.24</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2503.55</v>
+        <v>2521.08</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2363.1</v>
+        <v>2358.36</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5176.86</v>
+        <v>5166.48</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8451.139999999999</v>
+        <v>8402.219999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5295.89</v>
+        <v>5265.24</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,68 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3905.01</v>
+        <v>3859.58</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4371-338-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>7590.96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/lib-gral-bdo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4374-133-CM25</t>
+          <t>2675-198-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3728.62</v>
+        <v>2364.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4737-181-CM25</t>
+          <t>3690-200-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1125.76</v>
+        <v>2234.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3928-1170-CM25</t>
+          <t>594965-159-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5527.06</v>
+        <v>2140.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2776-937-CM25</t>
+          <t>2817-759-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1129.59</v>
+        <v>5418.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3863-531-CM25</t>
+          <t>1256505-260-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5685.7</v>
+        <v>5168.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3863-532-CM25</t>
+          <t>4737-181-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2957.12</v>
+        <v>1125.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3928-1263-CM25</t>
+          <t>4374-133-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1417.81</v>
+        <v>3728.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4164-549-CM25</t>
+          <t>3928-1170-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.080.600-2</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE DONIHUE</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2678.5</v>
+        <v>5527.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3014-281-CM25</t>
+          <t>2776-937-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1169.14</v>
+        <v>1129.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>997-180-CM25</t>
+          <t>3928-1263-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.488.070-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5028.06</v>
+        <v>1417.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2568-2235-CM25</t>
+          <t>3863-531-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3308.84</v>
+        <v>5685.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>615-80-CM25</t>
+          <t>3863-532-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>17874.45</v>
+        <v>2957.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>615-81-CM25</t>
+          <t>4164-549-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>69.080.600-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>I MUNICIPALIDAD DE DONIHUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5501.25</v>
+        <v>2678.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079563-459-CM25</t>
+          <t>3014-281-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8067.18</v>
+        <v>1169.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3928-1354-CM25</t>
+          <t>997-180-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INGENIERIA Y SEGURIDAD INDUSTRIAL KS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.488.070-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1794.37</v>
+        <v>5028.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2776-1010-CM25</t>
+          <t>2568-2235-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4832.27</v>
+        <v>3308.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>745-88-CM25</t>
+          <t>615-80-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.577.971-5</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6929.07</v>
+        <v>17874.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3690-360-CM25</t>
+          <t>615-81-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2701.98</v>
+        <v>5501.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>594965-224-CM25</t>
+          <t>1079563-459-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8376.389999999999</v>
+        <v>8067.18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1350767-127-CM25</t>
+          <t>3928-1354-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>917.5700000000001</v>
+        <v>1794.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1562-714-CM25</t>
+          <t>2776-1010-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3096.5</v>
+        <v>4832.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1469101-3-CM25</t>
+          <t>745-88-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>ENERGÍA DEL FUTURO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
+          <t>76.577.971-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>101307.36</v>
+        <v>6929.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3634-554-CM25</t>
+          <t>3690-360-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9398.959999999999</v>
+        <v>2701.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1562-724-CM25</t>
+          <t>594965-224-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7672.42</v>
+        <v>8376.389999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1562-731-CM25</t>
+          <t>1562-714-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA WAY SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.532.399-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2066.81</v>
+        <v>3096.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1562-732-CM25</t>
+          <t>1350767-127-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3774.2</v>
+        <v>917.5700000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3928-1465-CM25</t>
+          <t>1469101-3-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t xml:space="preserve">SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA  </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.795.374-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1259.74</v>
+        <v>101307.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>997-155-CM25</t>
+          <t>3634-554-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2616.87</v>
+        <v>9398.959999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1213444-638-CM25</t>
+          <t>1562-724-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27187.69</v>
+        <v>7672.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>598-347-CM25</t>
+          <t>1562-731-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6978.35</v>
+        <v>2066.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3810-7308-CM25</t>
+          <t>1562-732-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1666.45</v>
+        <v>3774.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1079563-496-CM25</t>
+          <t>3928-1465-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>Educación Municipal</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2643.58</v>
+        <v>1259.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1529-429-CM25</t>
+          <t>997-155-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1153.54</v>
+        <v>2616.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3033-17-CM25</t>
+          <t>1213444-638-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3174.4</v>
+        <v>27187.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4714-52-CM25</t>
+          <t>598-347-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>772.46</v>
+        <v>6978.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1208100-63-CM25</t>
+          <t>3810-7308-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>22625.5</v>
+        <v>1666.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2568-2292-CM25</t>
+          <t>1079563-496-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2811.29</v>
+        <v>2643.58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2568-2293-CM25</t>
+          <t>3033-17-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2786,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2330.67</v>
+        <v>3174.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2568-2291-CM25</t>
+          <t>4714-52-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8488.85</v>
+        <v>772.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1137833-275-CM25</t>
+          <t>1529-429-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>65.071.304-4</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1249.34</v>
+        <v>1153.54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1137833-276-CM25</t>
+          <t>1208100-63-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.071.304-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>793.39</v>
+        <v>22625.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>598-371-CM25</t>
+          <t>2568-2292-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6065.06</v>
+        <v>2811.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4737-3-CM26</t>
+          <t>2568-2293-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2118.12</v>
+        <v>2330.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1529-13-CM26</t>
+          <t>1137833-275-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>65.071.304-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8129.5</v>
+        <v>1249.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3690-27-CM26</t>
+          <t>1137833-276-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>65.071.304-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>CORPORACION DE LA CULTURA Y LAS ARTES DE LA ILUSTRE MUNICIPALIDAD DE R</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>14937.9</v>
+        <v>793.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3810-56-CM26</t>
+          <t>2568-2291-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4045.17</v>
+        <v>8488.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3810-57-CM26</t>
+          <t>598-371-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3872.77</v>
+        <v>6065.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3958-27-CM26</t>
+          <t>4737-3-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5520.36</v>
+        <v>2118.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2817-16-CM26</t>
+          <t>1529-13-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>28543.33</v>
+        <v>8129.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079563-20-CM26</t>
+          <t>3690-27-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9159.23</v>
+        <v>14937.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1079563-19-CM26</t>
+          <t>3810-56-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1778.17</v>
+        <v>4045.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3663-65-CM26</t>
+          <t>3810-57-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2879.16</v>
+        <v>3872.77</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3958-45-CM26</t>
+          <t>3958-27-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6002.05</v>
+        <v>5520.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2817-46-CM26</t>
+          <t>2817-16-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,17 +3757,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>28779.05</v>
+        <v>28543.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3810-84-CM26</t>
+          <t>1079563-20-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3133.63</v>
+        <v>9159.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1173480-8-CM26</t>
+          <t>3663-65-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>75.023.900-5</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP de Rengo</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1400.9</v>
+        <v>2879.16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1059082-3-CM26</t>
+          <t>1079563-19-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1450.56</v>
+        <v>1778.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3946-63-CM26</t>
+          <t>3958-45-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2655.93</v>
+        <v>6002.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3810-129-CM26</t>
+          <t>2817-46-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>823.74</v>
+        <v>28779.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2675-43-CM26</t>
+          <t>3810-84-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1099.14</v>
+        <v>3133.63</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3690-39-CM26</t>
+          <t>1173480-8-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,22 +4189,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>75.023.900-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>Centro de Educación y Trabajo CCP de Rengo</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4092</v>
+        <v>1400.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1529-48-CM26</t>
+          <t>1059082-3-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3823.87</v>
+        <v>1450.56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3014-49-CM26</t>
+          <t>3946-63-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2314.66</v>
+        <v>2655.93</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3810-173-CM26</t>
+          <t>3810-129-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2521.46</v>
+        <v>823.74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3690-48-CM26</t>
+          <t>2675-43-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1182.49</v>
+        <v>1099.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4590-1-CM26</t>
+          <t>3690-39-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>sociedad comercial aguad hnos y cia ltda</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.341.992-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1402.87</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2675-59-CM26</t>
+          <t>1529-48-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3979.51</v>
+        <v>3823.87</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3810-194-CM26</t>
+          <t>3014-49-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,27 +4611,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3474.35</v>
+        <v>2314.66</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2776-102-CM26</t>
+          <t>3810-173-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8643.07</v>
+        <v>2521.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4164-114-CM26</t>
+          <t>3690-48-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.080.600-2</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE DONIHUE</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3795.38</v>
+        <v>1182.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3033-8-CM26</t>
+          <t>2675-59-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,27 +4794,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4675.31</v>
+        <v>3979.51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2817-137-CM26</t>
+          <t>4590-1-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>sociedad comercial aguad hnos y cia ltda</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
+          <t>76.341.992-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1714.17</v>
+        <v>1402.87</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1529-72-CM26</t>
+          <t>2776-102-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1555.12</v>
+        <v>8643.07</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4737-17-CM26</t>
+          <t>3810-194-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1197.07</v>
+        <v>3474.35</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2776-124-CM26</t>
+          <t>4164-114-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.600-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE DONIHUE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>QUIMICA PASSOL S.A.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>84.634.200-1</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2549.2</v>
+        <v>3795.38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1213444-88-CM26</t>
+          <t>3033-8-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1270.18</v>
+        <v>4675.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2776-140-CM26</t>
+          <t>2817-137-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.378.846-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1095.56</v>
+        <v>1714.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3810-248-CM26</t>
+          <t>1529-72-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2960.03</v>
+        <v>1555.12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4737-18-CM26</t>
+          <t>4737-17-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>961.5</v>
+        <v>1197.07</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1350767-29-CM26</t>
+          <t>2776-124-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2113.34</v>
+        <v>2549.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1079563-71-CM26</t>
+          <t>1213444-88-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>818.54</v>
+        <v>1270.18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3946-132-CM26</t>
+          <t>2776-140-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,22 +5470,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>23588.32</v>
+        <v>1095.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1350767-30-CM26</t>
+          <t>3810-248-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.981.210-7</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3229.31</v>
+        <v>2960.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4737-21-CM26</t>
+          <t>4737-18-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2166.61</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4737-23-CM26</t>
+          <t>1350767-29-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1891.3</v>
+        <v>2113.34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4164-156-CM26</t>
+          <t>1079563-71-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,22 +5714,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.080.600-2</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE DONIHUE</t>
+          <t>SECCIÓN COMPRAS VI ZONA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5260.88</v>
+        <v>818.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2776-200-CM26</t>
+          <t>3946-132-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1222.04</v>
+        <v>23588.32</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1627-439-CM26</t>
+          <t>4737-21-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,27 +5831,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7940.35</v>
+        <v>2166.61</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1627-440-CM26</t>
+          <t>1350767-30-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.981.210-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>EJERCITO DE CHILE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>16345.08</v>
+        <v>3229.31</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4732-89-CM26</t>
+          <t>4737-23-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ARENTO SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.714.558-4</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1726.88</v>
+        <v>1891.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1529-102-CM26</t>
+          <t>4164-156-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,27 +6014,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.080.600-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE DONIHUE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>867.75</v>
+        <v>5260.88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2675-135-CM26</t>
+          <t>2776-200-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4172.17</v>
+        <v>1222.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4737-48-CM26</t>
+          <t>1627-439-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5361.55</v>
+        <v>7940.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4590-6-CM26</t>
+          <t>1627-440-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>22557.67</v>
+        <v>16345.08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2778-160-CM26</t>
+          <t>4732-89-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,22 +6263,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>ARENTO SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.714.558-4</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1852.11</v>
+        <v>1726.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2778-159-CM26</t>
+          <t>1529-102-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,22 +6324,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1019.8</v>
+        <v>867.75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2778-211-CM26</t>
+          <t>2675-135-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6784.23</v>
+        <v>4172.17</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1622-531-CM26</t>
+          <t>2778-159-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>EASY RETAIL S.A. .-</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>76.568.660-1</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>793.86</v>
+        <v>1019.8</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2778-232-CM26</t>
+          <t>2778-160-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4656.81</v>
+        <v>1852.11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4737-52-CM26</t>
+          <t>4590-6-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,22 +6568,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1076.24</v>
+        <v>22557.67</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2776-270-CM26</t>
+          <t>4737-48-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,22 +6629,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1249.2</v>
+        <v>5361.55</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3810-372-CM26</t>
+          <t>2778-211-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1810.17</v>
+        <v>6784.23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3634-187-CM26</t>
+          <t>1622-531-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>935.5</v>
+        <v>793.86</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>997-54-CM26</t>
+          <t>2778-232-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>16700.28</v>
+        <v>4656.81</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3863-142-CM26</t>
+          <t>4737-52-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>12132.96</v>
+        <v>1076.24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3810-406-CM26</t>
+          <t>3810-372-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>792.88</v>
+        <v>1810.17</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3634-197-CM26</t>
+          <t>2776-270-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6195.51</v>
+        <v>1249.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4737-66-CM26</t>
+          <t>3634-187-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3450.33</v>
+        <v>935.5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4737-73-CM26</t>
+          <t>997-54-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1050.26</v>
+        <v>16700.28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3730-276-CM26</t>
+          <t>3863-142-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.950.108-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4918.69</v>
+        <v>12132.96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2776-310-CM26</t>
+          <t>3810-406-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1245.99</v>
+        <v>792.88</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3690-154-CM26</t>
+          <t>3634-197-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4934.67</v>
+        <v>6195.51</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1529-151-CM26</t>
+          <t>4737-66-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>77.685.821-8</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1628.47</v>
+        <v>3450.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4732-137-CM26</t>
+          <t>4737-73-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3998.16</v>
+        <v>1050.26</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3810-515-CM26</t>
+          <t>3730-276-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3969.32</v>
+        <v>4918.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2776-365-CM26</t>
+          <t>2776-310-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6152.66</v>
+        <v>1245.99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>594965-91-CM26</t>
+          <t>3690-154-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7600,27 +7600,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CELGREN SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.529.681-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2372.45</v>
+        <v>4934.67</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4737-109-CM26</t>
+          <t>1529-151-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1129.5</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>730736-192-CM26</t>
+          <t>4732-137-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1620.62</v>
+        <v>3998.16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2675-265-CM26</t>
+          <t>3810-515-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,27 +7783,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>40761.31</v>
+        <v>3969.32</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3810-616-CM26</t>
+          <t>2776-365-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5153.2</v>
+        <v>6152.66</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3810-621-CM26</t>
+          <t>594965-91-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA CELGREN SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.529.681-K</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1031.77</v>
+        <v>2372.45</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3810-630-CM26</t>
+          <t>4737-109-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>5144.45</v>
+        <v>1129.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4371-259-CM26</t>
+          <t>730736-192-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2760.5</v>
+        <v>1620.62</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4371-260-CM26</t>
+          <t>2675-265-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8073.52</v>
+        <v>40761.31</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3946-286-CM26</t>
+          <t>3810-616-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2920.33</v>
+        <v>5153.2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2776-439-CM26</t>
+          <t>3810-621-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>842.8200000000001</v>
+        <v>1031.77</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2776-440-CM26</t>
+          <t>3810-630-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MAXVAL SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.290.944-6</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1758.87</v>
+        <v>5144.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2776-445-CM26</t>
+          <t>4371-259-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1009.31</v>
+        <v>2760.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2776-447-CM26</t>
+          <t>4371-260-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.206.192-9</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1772.24</v>
+        <v>8073.52</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3730-428-CM26</t>
+          <t>3946-286-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,22 +8459,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2521.08</v>
+        <v>2920.33</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4591-20-CM26</t>
+          <t>2776-439-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2358.36</v>
+        <v>842.8200000000001</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3810-662-CM26</t>
+          <t>2776-440-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MAXVAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.290.944-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5166.48</v>
+        <v>1758.87</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>594965-111-CM26</t>
+          <t>2776-445-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8402.219999999999</v>
+        <v>1009.31</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>745-29-CM26</t>
+          <t>2776-447-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.577.971-5</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5265.24</v>
+        <v>1772.24</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1562-273-CM26</t>
+          <t>3730-428-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3859.58</v>
+        <v>2521.08</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4371-338-CM26</t>
+          <t>4591-20-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8820,27 +8820,27 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,6 +8865,311 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
+        <v>2358.36</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>3810-662-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>MAXVAL SPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>77.290.944-6</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>5166.48</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>594965-111-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>8402.219999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>745-29-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>ENERGÍA DEL FUTURO</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>76.577.971-5</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>5265.24</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1562-273-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.702.000-9</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>3859.58</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4371-338-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
         <v>7590.96</v>
       </c>
     </row>
